--- a/Result/checkall/2025-12-14.xlsx
+++ b/Result/checkall/2025-12-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:CV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>

--- a/Result/checkall/2025-12-14.xlsx
+++ b/Result/checkall/2025-12-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV1"/>
+  <dimension ref="A1:CW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
